--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0179.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0179.xlsx
@@ -2784,7 +2784,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Ta còn chưa kịp ra tay giúp đỡ, Yangyang đã lao tới bảo vệ cậu như một...</t>
+          <t>Ta còn chưa kịp ra tay giúp đỡ, Dương Dương đã lao tới bảo vệ cậu như một...</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Ờ hừm, thôi kệ, Yangyang đang cố bảo vệ cậu, rồi BÙM! Tacet Discord đã bị xử lý trước khi tôi kịp nhìn rõ!</t>
+          <t>Ờ hừm, thôi kệ, Dương Dương đang cố bảo vệ cậu, rồi BÙM! Tacet Discord đã bị xử lý trước khi tôi kịp nhìn rõ!</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Rover, đưa ta Thiết bị đầu cuối của cậu một lát được không?</t>
+          <t>Rover, đưa tao Thiết bị đầu cuối của cậu một lát được không?</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Không tệ.</t>
+          <t>Khá đấy.</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Jinzhou nằm giữa Cao nguyên Desorock và Sa mạc Norfall. Là một thành phố biên giới và pháo đài. Nó đóng vai trò then chốt đối với sự an toàn của Huanglong.</t>
+          <t>Jinzhou nằm giữa Desorock Highland và Sa mạc Norfall. Là một thành phố biên giới và pháo đài. Nó đóng vai trò then chốt đối với sự an toàn của Huanglong.</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Theo như vở kịch &lt;ano=Những Vở Kịch Nổi Tiếng ở Tấn Châu&gt;Hero Plays&lt;/ano&gt; thì đúng rồi! Còn có khả năng đấy!</t>
+          <t>Theo như vở kịch &lt;ano=Popular Shows in Jinzhou&gt;Hero Plays&lt;/ano&gt; thì đúng rồi! Còn có khả năng đấy!</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Cậu biết không, {Male=anh ấy;Female=cô ấy} lúc đó tràn đầy năng lượng lắm! Đối phó với một Tổ Tacet khổng lồ mà vẫn hăng hái hơn tớ nhiều!</t>
+          <t>Cậu biết không, {Male=he;Female=she} lúc đó tràn đầy năng lượng lắm! Đối phó với một Tổ Tacet khổng lồ mà vẫn hăng hái hơn tớ nhiều!</t>
         </is>
       </c>
     </row>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Ta vẫn theo dõi tình trạng {Male=của cậu ấy;Female=của cô ấy} qua các Luồng...</t>
+          <t>Ta vẫn theo dõi tình trạng {Male=his;Female=her} qua các Luồng...</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Baizhi, ngươi biết đấy, tụi ta... ơ?</t>
+          <t>Baizhi, mày biết đấy, tụi tao... ơ?</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Chuyện gì đang xảy ra vậy?</t>
+          <t>Có chuyện gì vậy?</t>
         </is>
       </c>
     </row>
@@ -7529,7 +7529,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Các chỉ số sinh tồn của {Male=anh ấy;Female:cô ấy} ổn định, đồng tử kích thước bình thường, nhịp thở đều đặn.</t>
+          <t>Các chỉ số sinh tồn của {Male=His;Female=Her} ổn định, đồng tử kích thước bình thường, nhịp thở đều đặn.</t>
         </is>
       </c>
     </row>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Rover đang ở bên ta... và cả Tacet Discord kỳ lạ kia nữa.</t>
+          <t>Vận Mệnh Giả đang ở bên ta... và cả Tacet Discord kỳ lạ kia nữa.</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Thôi mà, đừng khiêm tốn thế chứ! Lúc nãy cậu còn chưa dùng hết sức đấy. Ta đã tận mắt thấy cậu hạ gục tên đó như thế nào rồi!</t>
+          <t>Thôi mà, đừng khiêm tốn thế chứ! Lúc nãy cậu còn chưa dùng hết sức đấy. Tao đã tận mắt thấy cậu hạ gục tên đó như thế nào rồi!</t>
         </is>
       </c>
     </row>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Xin lỗi. Chúng ta hơi quá tay rồi. "Reverberation" hay "Echo" có gợi nhớ gì với cậu không, Rover?</t>
+          <t>Xin lỗi. Chúng ta hơi quá tay rồi. "Reverberation" hay "Echo" có gợi nhớ gì với cậu không, Vận Mệnh Giả?</t>
         </is>
       </c>
     </row>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>À, cái Pangu Terminal mà cô ấy nói là thiết bị hình bầu bầu mà mọi Cộng Hưởng Giả đều có, do các nhà nghiên cứu ở Huanglong phát triển đấy!</t>
+          <t>À, cái Pangu Terminal mà cô ấy nói là thiết bị hình bầu bầu mà mọi Resonator đều có, do các nhà nghiên cứu ở Huanglong phát triển đấy!</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Ngươi giả điên giả ngốc từ đầu à?</t>
+          <t>Mày giả điên giả ngốc từ đầu à?</t>
         </is>
       </c>
     </row>
@@ -11299,7 +11299,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Giờ ta lại càng tò mò hơn... Dù sao thì đồ cay vẫn là nhất!</t>
+          <t>Giờ tao lại càng tò mò hơn... Dù sao thì đồ cay vẫn là nhất!</t>
         </is>
       </c>
     </row>
@@ -12339,7 +12339,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Yangyang nhớ vanh vách những văn bản cổ xưa. Còn ta? Ta chỉ nhớ đại khái nội dung câu chuyện thôi.</t>
+          <t>Yangyang nhớ vanh vách những văn bản cổ xưa. Còn tao? Tao chỉ nhớ đại khái nội dung câu chuyện thôi.</t>
         </is>
       </c>
     </row>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Hay là Rover chính là tổ tiên xa xưa của tất cả chúng ta? {Male=Ông cố cố cố cố;Female=Bà cố cố cố cố} ấy?</t>
+          <t>Hay là Rover chính là tổ tiên xa xưa của tất cả chúng ta? {Male=granddaddy;Female=granny} ấy?</t>
         </is>
       </c>
     </row>
@@ -13444,7 +13444,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Trong số vô vàn vị khách đến thăm, có một &lt;color=Highlight&gt;visitor&lt;/color&gt; đặc biệt quan trọng nhất đối với ta, với Thành Jinzhou, và với toàn bộ Huanglong.</t>
+          <t>Trong số vô vàn vị khách đến thăm, có một &lt;color=Highlight&gt;vị khách&lt;/color&gt; đặc biệt quan trọng nhất đối với ta, với Thành Jinzhou, và với toàn bộ Huanglong.</t>
         </is>
       </c>
     </row>
@@ -13704,7 +13704,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Nếu cậu định ở lại Kim Châu một thời gian, tôi sẽ rất vui được đích thân gặp cậu tại Tòa Thị Chính Kim Châu.</t>
+          <t>Nếu cậu định ở lại Jinzhou một thời gian, tôi sẽ rất vui được đích thân gặp cậu tại Tòa Thị Chính Jinzhou.</t>
         </is>
       </c>
     </row>
@@ -13899,7 +13899,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Vậy nên, ta mong muốn người dân và binh lính của Kim Châu sẽ hỗ trợ vị khách quý này khi có cơ hội.</t>
+          <t>Vậy nên, ta mong muốn người dân và binh lính của Jinzhou sẽ hỗ trợ vị khách quý này khi có cơ hội.</t>
         </is>
       </c>
     </row>
@@ -13964,7 +13964,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Sao tự dưng ta lại có cảm giác này...</t>
+          <t>Sao tự dưng tao lại có cảm giác này...</t>
         </is>
       </c>
     </row>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Ồ, thì ra đây mới là sức mạnh thật sự của một Thủ Lĩnh... Ý mình là của Rover chúng ta!</t>
+          <t>Ồ, thì ra đây mới là sức mạnh thật sự của một Thủ Lĩnh... Ý mình là của Vận Mệnh Giả chúng ta!</t>
         </is>
       </c>
     </row>
@@ -15069,7 +15069,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Giờ cậu định làm gì, Rover?</t>
+          <t>Giờ cậu định làm gì, Vận Mệnh Giả?</t>
         </is>
       </c>
     </row>
@@ -15719,7 +15719,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Dù cậu có phải là vị khách mà Quan Phủ nhắc đến hay không, chắc chắn cậu rất quan trọng với Kim Châu, và cậu sẽ là... quan trọng của chúng tôi.</t>
+          <t>Dù cậu có phải là vị khách mà Quan Phủ nhắc đến hay không, chắc chắn cậu rất quan trọng với Jinzhou, và cậu sẽ là... quan trọng của chúng tôi.</t>
         </is>
       </c>
     </row>
@@ -15849,7 +15849,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Dù sao thì khi trở về Kim Châu, mình sẽ đãi cậu món đặc sản nổi tiếng ở Nhà hàng Panhua.</t>
+          <t>Dù sao thì khi trở về Jinzhou, mình sẽ đãi cậu món đặc sản nổi tiếng ở Nhà hàng Panhua.</t>
         </is>
       </c>
     </row>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Ta sẽ kiếm cho ngươi một cái để hấp thụ. Ta chưa bao giờ thất hứa đâu! Anh hùng Chixia của ngươi đang săn lùng đây!</t>
+          <t>Tao sẽ kiếm cho mày một cái để hấp thụ. Tao chưa bao giờ thất hứa đâu! Anh hùng Chixia của mày đang săn lùng đây!</t>
         </is>
       </c>
     </row>
@@ -18839,7 +18839,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Ý bạn là gì?</t>
+          <t>Ý anh là sao?</t>
         </is>
       </c>
     </row>
@@ -19294,7 +19294,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Okay.</t>
+          <t>Ừ.</t>
         </is>
       </c>
     </row>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Nếu có gì thắc mắc, vừa đi vừa nói cũng được. Ta với Yangyang sẽ kể cho cậu nghe tường tận từ đầu đến cuối!</t>
+          <t>Nếu có gì thắc mắc, vừa đi vừa nói cũng được. Tao với Yangyang sẽ kể cho cậu nghe tường tận từ đầu đến cuối!</t>
         </is>
       </c>
     </row>
@@ -19749,7 +19749,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Rover, tôi biết cậu chẳng nhớ gì cả, nhưng có một điều tôi chắc chắn 90%... không, 100% luôn! Cậu cũng phải là một Cộng Hưởng Giả.</t>
+          <t>Rover, tôi biết cậu chẳng nhớ gì cả, nhưng có một điều tôi chắc chắn 90%... không, 100% luôn! Cậu cũng phải là một Resonator.</t>
         </is>
       </c>
     </row>
@@ -19879,7 +19879,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Hơn nữa, chẳng mấy ai còn lang thang nơi hoang dã này nữa, trừ khi là Cộng Hưởng Giả.</t>
+          <t>Hơn nữa, chẳng mấy ai còn lang thang nơi hoang dã này nữa, trừ khi là Resonator.</t>
         </is>
       </c>
     </row>
@@ -19944,7 +19944,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Rover, tôi biết cậu chẳng nhớ gì cả, nhưng có một điều tôi chắc chắn 90%... không, 100% luôn! Cậu cũng phải là một Cộng Hưởng Giả.</t>
+          <t>Rover, tôi biết cậu chẳng nhớ gì cả, nhưng có một điều tôi chắc chắn 90%... không, 100% luôn! Cậu cũng phải là một Resonator.</t>
         </is>
       </c>
     </row>
@@ -20009,7 +20009,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Hơn nữa, chẳng mấy ai còn lang thang nơi hoang dã này nữa, trừ khi là Cộng Hưởng Giả.</t>
+          <t>Hơn nữa, chẳng mấy ai còn lang thang nơi hoang dã này nữa, trừ khi là Resonator.</t>
         </is>
       </c>
     </row>
@@ -21829,7 +21829,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Tại sao?</t>
+          <t>Sao vậy?</t>
         </is>
       </c>
     </row>
@@ -22609,7 +22609,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Dù sao thì ta đã nghe câu đó cả triệu lần rồi, có muốn quên cũng không quên được. Dù ông có quên thì ta vẫn nhớ thêm mấy chục năm nữa.</t>
+          <t>Dù sao thì tao đã nghe câu đó cả triệu lần rồi, có muốn quên cũng không quên được. Dù ông có quên thì tao vẫn nhớ thêm mấy chục năm nữa.</t>
         </is>
       </c>
     </row>
@@ -22739,7 +22739,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Thật sao?</t>
+          <t>Thật chứ?</t>
         </is>
       </c>
     </row>
@@ -24299,7 +24299,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Vậy thì ta sẽ đi nộp báo cáo, và chuẩn bị tài liệu cần thiết cho buổi tiếp kiến của Rover với Quan Phán trong lúc đó.</t>
+          <t>Vậy thì ta sẽ đi nộp báo cáo, và chuẩn bị tài liệu cần thiết cho buổi tiếp kiến của Vận Mệnh Giả với Quan Phán trong lúc đó.</t>
         </is>
       </c>
     </row>
@@ -24494,7 +24494,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Còn ta thì sao?</t>
+          <t>Còn tao thì sao?</t>
         </is>
       </c>
     </row>
@@ -24559,7 +24559,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Okay.</t>
+          <t>Ừ.</t>
         </is>
       </c>
     </row>
@@ -24819,7 +24819,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Vậy thì ta sẽ đưa Rover đến Tháp Nexus đăng ký trước, rồi chúng ta sẽ đi chơi đâu đó một lát.</t>
+          <t>Vậy thì tao sẽ đưa Vận Mệnh Giả đến Tháp Nexus đăng ký trước, rồi chúng ta sẽ đi chơi đâu đó một lát.</t>
         </is>
       </c>
     </row>
@@ -24884,7 +24884,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Mới đến Jinzhou mà để {Male=cậu ấy;Female=cô ấy} đứng ngoài Tòa Thị Chính không có việc gì làm thì không ổn rồi.</t>
+          <t>Mới đến Jinzhou mà để {Male=he;Female=she} đứng ngoài Tòa Thị Chính không có việc gì làm thì không ổn rồi.</t>
         </is>
       </c>
     </row>
@@ -25079,7 +25079,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Để tôi lo!</t>
+          <t>Để đó cho tôi!</t>
         </is>
       </c>
     </row>
@@ -25404,7 +25404,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Chắc chắn rồi.</t>
+          <t>Được thôi.</t>
         </is>
       </c>
     </row>
@@ -25729,7 +25729,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Baizhi, ta nghĩ câu cuối của ngươi nên diễn đạt lại cho hay hơn...</t>
+          <t>Baizhi, tao nghĩ câu cuối của mày nên diễn đạt lại cho hay hơn...</t>
         </is>
       </c>
     </row>
@@ -25924,7 +25924,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Còn chần chừ gì nữa. Xuất phát thôi, để ta còn dẫn Rover đi dạo chơi!</t>
+          <t>Còn chần chừ gì nữa. Xuất phát thôi, để tao còn dẫn Rover đi dạo chơi!</t>
         </is>
       </c>
     </row>
@@ -26639,7 +26639,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Có gì tôi có thể giúp cậu không, Rover?</t>
+          <t>Có gì tôi có thể giúp cậu không, Vận Mệnh Giả?</t>
         </is>
       </c>
     </row>
@@ -27289,7 +27289,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Đa số binh lính ngày nay đều là Cộng Hưởng Giả cả.</t>
+          <t>Đa số binh lính ngày nay đều là Resonator cả.</t>
         </is>
       </c>
     </row>
@@ -28004,7 +28004,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Nhưng... đây là những gì ta hiểu từ những gì cô ấy kể. Ta chỉ gặp Sentinel của chúng ta vài lần thôi.</t>
+          <t>Nhưng... đây là những gì tao hiểu từ những gì cô ấy kể. Tao chỉ gặp Sentinel của chúng ta vài lần thôi.</t>
         </is>
       </c>
     </row>
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Còn tùy vào quyết định của cậu, Rover à.</t>
+          <t>Còn tùy vào quyết định của cậu, Vận Mệnh Giả à.</t>
         </is>
       </c>
     </row>
@@ -29499,7 +29499,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Chuyện gì đang xảy ra vậy?</t>
+          <t>Có chuyện gì vậy?</t>
         </is>
       </c>
     </row>
@@ -29889,7 +29889,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Hơn nữa... Rover bí ẩn kia!</t>
+          <t>Hơn nữa... Vận Mệnh Giả bí ẩn kia!</t>
         </is>
       </c>
     </row>
@@ -32034,7 +32034,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Kẹo sao? Ôi! Ta nhớ hồi nhỏ ta ăn mấy viên này. Chắc gọi là... ngọc đường nhỉ?</t>
+          <t>Kẹo sao? Ôi! Tao nhớ hồi nhỏ tao ăn mấy viên này. Chắc gọi là... ngọc đường nhỉ?</t>
         </is>
       </c>
     </row>
